--- a/02Excel/05Lookup_Functions.xlsx
+++ b/02Excel/05Lookup_Functions.xlsx
@@ -5,22 +5,20 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\DA_07_batch\02Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\DA_12_Batch\02Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EC6973-E393-410E-B2B5-C5193F72A5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C57FB54-695D-42B4-992A-876265E8FA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VLOOKUP_Basics" sheetId="1" r:id="rId1"/>
-    <sheet name="HLOOKUP_Basics" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="11" r:id="rId3"/>
+    <sheet name="Ref" sheetId="12" r:id="rId1"/>
+    <sheet name="VLOOKUP_Basics" sheetId="1" r:id="rId2"/>
+    <sheet name="HLOOKUP_Basics" sheetId="2" r:id="rId3"/>
     <sheet name="XLOOKUP_Basics" sheetId="3" r:id="rId4"/>
     <sheet name="Another" sheetId="7" r:id="rId5"/>
-    <sheet name="Challenge_Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Task" sheetId="9" r:id="rId7"/>
-    <sheet name="Index match" sheetId="10" r:id="rId8"/>
+    <sheet name="Task" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XLOOKUP_Basics!$A$1:$A$12</definedName>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="71">
   <si>
     <t>ProductID</t>
   </si>
@@ -165,9 +163,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Task</t>
-  </si>
-  <si>
     <t>What to Find:</t>
   </si>
   <si>
@@ -201,9 +196,6 @@
     <t>HLOOKUP($F$5,$A$1:$E$3,COLUMNS($F$4:G4),0)</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>E101</t>
   </si>
   <si>
@@ -213,19 +205,10 @@
     <t>E103</t>
   </si>
   <si>
-    <t>Charlie</t>
-  </si>
-  <si>
     <t>E104</t>
   </si>
   <si>
-    <t>Diana</t>
-  </si>
-  <si>
     <t>E105</t>
-  </si>
-  <si>
-    <t>Edward</t>
   </si>
   <si>
     <t>Location</t>
@@ -293,25 +276,13 @@
   </si>
   <si>
     <t>Bonus Amount</t>
-  </si>
-  <si>
-    <t>INDEX(return_range, MATCH(lookup_value, lookup_range, 0))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match </t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>Index+Match</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,17 +311,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -465,13 +425,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -499,6 +458,32 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -514,46 +499,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -893,18 +840,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4708C163-774F-46AC-B7B7-78108186313E}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>5</v>
+      </c>
+      <c r="C1">
+        <f>A1+B1</f>
+        <v>6</v>
+      </c>
+      <c r="D1">
+        <f>A1+H$2</f>
+        <v>21</v>
+      </c>
+      <c r="E1">
+        <f t="shared" ref="E1:F1" si="0">B1+I$2</f>
+        <v>30</v>
+      </c>
+      <c r="F1">
+        <f>C1+J$2</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C12" si="1">A2+B2</f>
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:D11" si="2">A2+H$2</f>
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <f>A5+B5</f>
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <f>A12+B12</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="4" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="4"/>
-    <col min="7" max="7" width="15.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="3"/>
+    <col min="7" max="7" width="15.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -921,121 +1083,122 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>101</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>102</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3">
+        <v>102</v>
+      </c>
+      <c r="G3" s="22" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>101</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>103</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>104</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6">
+        <v>104</v>
+      </c>
+      <c r="H5" s="8">
+        <f>VLOOKUP(G5,A1:D5,3,0)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <f>COLUMNS($A$7:A7)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <f>COLUMNS($A$7:B7)</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="3">
+        <f>COLUMNS($A$7:C7)</f>
+        <v>3</v>
+      </c>
+      <c r="D8" s="3">
+        <f>COLUMNS($A$7:D7)</f>
         <v>4</v>
       </c>
-      <c r="C2" s="5">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>102</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5">
-        <v>25</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="13" t="s">
+      <c r="G8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>103</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>104</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="7">
-        <v>102</v>
-      </c>
-      <c r="H5" s="9">
-        <f>VLOOKUP(G5,A1:D5,3,0)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <f>COLUMNS($A$6:A6)</f>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="G9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B7" s="4">
-        <f>COLUMNS($A$6:B6)</f>
-        <v>2</v>
-      </c>
-      <c r="C7" s="4">
-        <f>COLUMNS($A$6:C6)</f>
-        <v>3</v>
-      </c>
-      <c r="D7" s="4">
-        <f>COLUMNS($A$6:D6)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="G9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1051,39 +1214,43 @@
       <c r="D10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="7">
-        <v>107</v>
-      </c>
-      <c r="H10" s="7" t="str">
-        <f>IFERROR(VLOOKUP(G10,A1:D5,4,0),"Not found")</f>
-        <v>Not found</v>
+      <c r="G10" s="6">
+        <v>108</v>
+      </c>
+      <c r="H10" s="8" t="str">
+        <f>IFERROR(VLOOKUP(G10,A1:D5,2,0),"Not Found")</f>
+        <v>Not Found</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>104</v>
-      </c>
-      <c r="B11" s="9" t="str">
+      <c r="A11" s="6">
+        <v>101</v>
+      </c>
+      <c r="B11" s="8" t="str">
         <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:B10),0)</f>
-        <v>Marker</v>
-      </c>
-      <c r="C11" s="9">
+        <v>Pen</v>
+      </c>
+      <c r="C11" s="8">
         <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:C10),0)</f>
-        <v>15</v>
-      </c>
-      <c r="D11" s="9" t="str">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="str">
         <f>VLOOKUP($A$11,$A$1:$D$5,COLUMNS($A$10:D10),0)</f>
         <v>Stationery</v>
       </c>
+      <c r="H11" s="3" t="e">
+        <f>VLOOKUP(G10,A1:D5,2,0)</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1101,7 +1268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1112,61 +1279,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>500</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>700</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>600</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>5</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>2</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="F3" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F4" s="1" t="s">
@@ -1175,19 +1342,19 @@
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <f>HLOOKUP($F$5,$A$1:$E$3,COLUMNS($F$4:G4),0)</f>
         <v>800</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <f>HLOOKUP($F$5,$A$1:$E$3,COLUMNS($F$4:H4),0)</f>
         <v>4</v>
       </c>
@@ -1199,13 +1366,13 @@
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="F7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
@@ -1254,29 +1421,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7D58DE-DF00-42D1-94A3-E7AA3C802BB9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="4"/>
-    <col min="7" max="7" width="13.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="3"/>
+    <col min="7" max="7" width="13.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1297,41 +1455,41 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>201</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>50000</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="G2" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>202</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>60000</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1342,59 +1500,59 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>203</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>55000</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>208</v>
       </c>
-      <c r="H4" s="7" t="str">
-        <f>_xlfn.XLOOKUP(G4,A2:A5,B2:B5,"Not found")</f>
-        <v>Not found</v>
+      <c r="H4" s="6" t="str">
+        <f>_xlfn.XLOOKUP(G4,A2:A5,B2:B5,"Not Found")</f>
+        <v>Not Found</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>204</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>58000</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="G6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="A7" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
       <c r="G7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1418,44 +1576,44 @@
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="7">
-        <f>_xlfn.XLOOKUP(G8,B2:B5,D2:D5,"Not found")</f>
+      <c r="H8" s="6">
+        <f>_xlfn.XLOOKUP(G8,B2:B5,D2:D5)</f>
         <v>55000</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>201</v>
-      </c>
-      <c r="B9" s="7" t="str" cm="1">
-        <f t="array" ref="B9:E9">_xlfn.XLOOKUP(A9,A2:A5,B2:E5)</f>
-        <v>Alice</v>
-      </c>
-      <c r="C9" s="8" t="str">
-        <v>HR</v>
-      </c>
-      <c r="D9" s="8">
-        <v>50000</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <v>2023-01-10</v>
+      <c r="A9" s="6">
+        <v>202</v>
+      </c>
+      <c r="B9" s="6" t="str" cm="1">
+        <f t="array" ref="B9:E9">_xlfn.XLOOKUP(A9,A2:A5,B2:E5,"Not Found")</f>
+        <v>Bob</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="D9" s="7">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <v>2022-11-05</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1480,12 +1638,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="A1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1502,19 +1660,19 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>103</v>
       </c>
-      <c r="B3" s="28" t="str">
-        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(Another!$A$2:B2),0)</f>
+      <c r="B3" s="19" t="str">
+        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(VLOOKUP_Basics!$A$1:B1),0)</f>
         <v>Eraser</v>
       </c>
-      <c r="C3" s="28">
-        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(Another!$A$2:C2),0)</f>
+      <c r="C3" s="19">
+        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(VLOOKUP_Basics!$A$1:C1),0)</f>
         <v>5</v>
       </c>
-      <c r="D3" s="28" t="str">
-        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(Another!$A$2:D2),0)</f>
+      <c r="D3" s="19" t="str">
+        <f>VLOOKUP($A$3,VLOOKUP_Basics!$A$1:$D$5,COLUMNS(VLOOKUP_Basics!$A$1:D1),0)</f>
         <v>Stationery</v>
       </c>
     </row>
@@ -1524,268 +1682,22 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EAB3B296-705D-4257-B296-CC7470E8BFFF}">
+          <x14:formula1>
+            <xm:f>VLOOKUP_Basics!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="J2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <f>SUM(G3,$J$2)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H12" si="0">SUM(G4,$J$2)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="2">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="2">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C8" s="2">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2">
-        <v>30</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C9" s="2">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2">
-        <v>28</v>
-      </c>
-      <c r="G9" s="2">
-        <v>35</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C10" s="2">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2">
-        <v>16</v>
-      </c>
-      <c r="E10" s="2">
-        <v>24</v>
-      </c>
-      <c r="F10" s="2">
-        <v>32</v>
-      </c>
-      <c r="G10" s="2">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C11" s="2">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2">
-        <v>36</v>
-      </c>
-      <c r="G11" s="2">
-        <v>45</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="2">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2">
-        <v>30</v>
-      </c>
-      <c r="F12" s="2">
-        <v>40</v>
-      </c>
-      <c r="G12" s="2">
-        <v>50</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v>55</v>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v>110</v>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v>165</v>
-      </c>
-      <c r="F13">
-        <f t="shared" ref="F13:G13" si="1">SUM(F3:F12)</f>
-        <v>220</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>275</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD803EC-73F3-4807-A24B-D5D650856789}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1809,297 +1721,259 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="12">
+        <v>45000</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2019</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="12">
+        <v>52000</v>
+      </c>
+      <c r="F3" s="12">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="12">
+        <v>65000</v>
+      </c>
+      <c r="F4" s="12">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="12">
+        <v>58000</v>
+      </c>
+      <c r="F5" s="12">
+        <v>2017</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="M5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="12">
+        <v>48000</v>
+      </c>
+      <c r="F6" s="12">
+        <v>2021</v>
+      </c>
+      <c r="O6" t="e">
+        <f>VLOOKUP($M$6,$A$1:$F$9,5,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P6" s="21" t="e">
+        <f>HLOOKUP(N6,H1:M2,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q6" t="e">
+        <f>O6*P6</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="12">
+        <v>62000</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="12">
+        <v>47000</v>
+      </c>
+      <c r="F8" s="12">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="C9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="12">
+        <v>54000</v>
+      </c>
+      <c r="F9" s="12">
+        <v>2016</v>
+      </c>
+      <c r="H9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="20">
-        <v>45000</v>
-      </c>
-      <c r="F2" s="20">
-        <v>2019</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="J2" s="22">
-        <v>0.08</v>
-      </c>
-      <c r="K2" s="22">
-        <v>0.12</v>
-      </c>
-      <c r="L2" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="M2" s="22">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="20">
-        <v>52000</v>
-      </c>
-      <c r="F3" s="20">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="20">
-        <v>65000</v>
-      </c>
-      <c r="F4" s="20">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="20">
-        <v>58000</v>
-      </c>
-      <c r="F5" s="20">
-        <v>2017</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="20">
-        <v>48000</v>
-      </c>
-      <c r="F6" s="20">
-        <v>2021</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6">
-        <f>VLOOKUP(I6,A1:F9,5,0)</f>
-        <v>58000</v>
-      </c>
-      <c r="M6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" t="str">
-        <f>VLOOKUP($M$6,$A$1:$F$9,3,0)</f>
-        <v>IT</v>
-      </c>
-      <c r="O6">
-        <f>VLOOKUP($M$6,$A$1:$F$9,5,0)</f>
-        <v>65000</v>
-      </c>
-      <c r="P6" s="30">
-        <f>HLOOKUP(N6,H1:M2,2,0)</f>
-        <v>0.12</v>
-      </c>
-      <c r="Q6">
-        <f>O6*P6</f>
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="20">
-        <v>62000</v>
-      </c>
-      <c r="F7" s="20">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+    </row>
+    <row r="10" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="I10" s="18"/>
+    </row>
+    <row r="13" spans="1:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="20">
-        <v>47000</v>
-      </c>
-      <c r="F8" s="20">
-        <v>2020</v>
-      </c>
-      <c r="L8">
-        <f>VLOOKUP(I6,A1:F9,5,0) * HLOOKUP(I9,H1:M2,2,0)</f>
-        <v>8700</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="20">
-        <v>54000</v>
-      </c>
-      <c r="F9" s="20">
-        <v>2016</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H10" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="27">
-        <f>HLOOKUP(I9,H1:M2,2,0)</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="I13">
-        <f>J6*I10</f>
-        <v>8700</v>
-      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2108,150 +1982,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B102B2-F93F-4FE6-AA26-382ABB013726}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="19">
-        <v>50000</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="str">
-        <f>INDEX(C2:C6,3)</f>
-        <v>Finance</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="19">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="19">
-        <v>55000</v>
-      </c>
-      <c r="F4" s="31"/>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="19">
-        <v>70000</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5">
-        <f>MATCH(H2,C2:C6,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="19">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9">
-        <f>INDEX(D2:D6,MATCH(E8,A2:A6,0))</f>
-        <v>50000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="str">
-        <f>INDEX(A2:A6,MATCH(G9,B2:B6,0))</f>
-        <v>E102</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>